--- a/outputs/55979.xlsx
+++ b/outputs/55979.xlsx
@@ -356,48 +356,52 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -653,65 +657,65 @@
   <dimension ref="A6:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH($A$10,Supplier_1!$A$2:$A$10,0)),"Supplier_1",IF(ISNUMBER(MATCH($A$10,Supplier_2!$A$2:$A$10,0)),"Supplier_2",IF(ISNUMBER(MATCH($A$10,Supplier_3!$A$2:$A$10,0)),"Supplier_3","")))</f>
+      <c r="B7" s="3" t="str">
+        <f aca="false">IF(COUNTIF(Supplier_1!$A$2:$A$10,$A$10)&gt;0,"Supplier_1",IF(COUNTIF(Supplier_2!$A$2:$A$10,$A$10)&gt;0,"Supplier_2",IF(COUNTIF(Supplier_3!$A$2:$A$10,$A$10)&gt;0,"Supplier_3","")))</f>
         <v>Supplier_1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="str">
+      <c r="B10" s="7" t="str">
         <f aca="false">IFERROR(VLOOKUP($A$10,Supplier_1!A2:D10,2,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_2!A2:D10,2,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_3!A2:D10,2,FALSE()),"")))</f>
         <v>TEST 7</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <f aca="false">IFERROR(VLOOKUP($A$10,Supplier_1!A2:D10,3,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_2!A2:D10,3,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_3!A2:D10,3,FALSE()),"")))</f>
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <f aca="false">IFERROR(VLOOKUP($A$10,Supplier_1!A2:D10,4,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_2!A2:D10,4,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_3!A2:D10,4,FALSE()),"")))</f>
         <v>65</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="8" t="n">
         <f aca="false">IFERROR(VLOOKUP($C$10,Discount_S1!A2:B5,2,FALSE()),IFERROR(VLOOKUP($C$10,Discount_S2!A2:B5,2,FALSE()),IFERROR(VLOOKUP($C$10,Discount_S3!A2:B5,2,FALSE()),"")))</f>
         <v>0.25</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <f aca="false">D10*(1-E10)</f>
         <v>48.75</v>
       </c>
@@ -735,148 +739,148 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>34</v>
       </c>
     </row>
@@ -899,148 +903,148 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1063,149 +1067,149 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1229,34 +1233,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1280,34 +1284,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -1331,34 +1335,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.18</v>
       </c>
     </row>

--- a/outputs/55979.xlsx
+++ b/outputs/55979.xlsx
@@ -671,8 +671,8 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="str">
-        <f aca="false">IF(COUNTIF(Supplier_1!$A$2:$A$10,$A$10)&gt;0,"Supplier_1",IF(COUNTIF(Supplier_2!$A$2:$A$10,$A$10)&gt;0,"Supplier_2",IF(COUNTIF(Supplier_3!$A$2:$A$10,$A$10)&gt;0,"Supplier_3","")))</f>
-        <v>Supplier_1</v>
+        <f aca="false">IFERROR(VLOOKUP($A$10,Supplier_1!A2:B10,2,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_2!A2:B10,2,FALSE()),IFERROR(VLOOKUP($A$10,Supplier_3!A2:B10,2,FALSE()),"")))</f>
+        <v>TEST 7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
